--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5148514851485149</v>
+        <v>0.4646464646464646</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4718309859154929</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="D2">
-        <v>0.5905511811023622</v>
+        <v>0.640625</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
